--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -510,94 +510,94 @@
   </numFmts>
   <fonts count="13">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <u val="single"/>
+      <sz val="16"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="16"/>
-      <u val="single"/>
     </font>
     <font>
+      <b val="1"/>
+      <u val="single"/>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="12"/>
-      <u val="single"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="28"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="72"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="72"/>
     </font>
     <font>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="100"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="100"/>
     </font>
     <font>
+      <sz val="110"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="110"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="250"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="250"/>
     </font>
   </fonts>
   <fills count="6">
@@ -2110,16 +2110,16 @@
         <v>24</v>
       </c>
       <c r="D2" s="3">
-        <v>0.0020833333333333333</v>
+        <v>0.00208333333333333</v>
       </c>
       <c r="E2" s="3" t="str">
         <f>(A2*B2*C2*D2)</f>
       </c>
       <c r="F2" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G2" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H2" s="31" t="str">
         <f>C2*I2+J2</f>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>0.0020833333333333333</v>
+        <v>0.00208333333333333</v>
       </c>
       <c r="E3" s="3" t="str">
         <f>(A3*B3*C3*D3)</f>
       </c>
       <c r="F3" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G3" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H3" s="3" t="str">
         <f>E3+(A3*C3*F3)+G3</f>
@@ -2214,16 +2214,16 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="3">
-        <v>0.002777777777777778</v>
+        <v>0.00277777777777777</v>
       </c>
       <c r="E8" s="3" t="str">
         <f>(A8*B8*D8)</f>
       </c>
       <c r="F8" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G8" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H8" s="31" t="str">
         <f>E8+(A8*F8)+G8</f>
